--- a/artfynd/A 38156-2026 artfynd.xlsx
+++ b/artfynd/A 38156-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136067673</v>
       </c>
       <c r="B2" t="n">
-        <v>92327</v>
+        <v>92330</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136580334</v>
       </c>
       <c r="B3" t="n">
-        <v>89274</v>
+        <v>89276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38156-2026 artfynd.xlsx
+++ b/artfynd/A 38156-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136067673</v>
       </c>
       <c r="B2" t="n">
-        <v>92330</v>
+        <v>92331</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38156-2026 artfynd.xlsx
+++ b/artfynd/A 38156-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136580334</v>
       </c>
       <c r="B3" t="n">
-        <v>89276</v>
+        <v>89278</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38156-2026 artfynd.xlsx
+++ b/artfynd/A 38156-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136580334</v>
       </c>
       <c r="B3" t="n">
-        <v>89278</v>
+        <v>89280</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38156-2026 artfynd.xlsx
+++ b/artfynd/A 38156-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136580334</v>
       </c>
       <c r="B3" t="n">
-        <v>89280</v>
+        <v>89282</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38156-2026 artfynd.xlsx
+++ b/artfynd/A 38156-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136580334</v>
       </c>
       <c r="B3" t="n">
-        <v>89282</v>
+        <v>89284</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38156-2026 artfynd.xlsx
+++ b/artfynd/A 38156-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136580334</v>
       </c>
       <c r="B3" t="n">
-        <v>89284</v>
+        <v>89285</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38156-2026 artfynd.xlsx
+++ b/artfynd/A 38156-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136580334</v>
       </c>
       <c r="B3" t="n">
-        <v>89285</v>
+        <v>89291</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38156-2026 artfynd.xlsx
+++ b/artfynd/A 38156-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136580334</v>
       </c>
       <c r="B3" t="n">
-        <v>89291</v>
+        <v>89295</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38156-2026 artfynd.xlsx
+++ b/artfynd/A 38156-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ23"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>136067673</v>
+        <v>137169955</v>
       </c>
       <c r="B2" t="n">
-        <v>92331</v>
+        <v>89176</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3298</v>
+        <v>3295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Hagfingersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Clavulinopsis helvola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Pers.) Corner</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -745,22 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,16 +786,16 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136067673</t>
+          <t>https://artportalen.se/Sighting/137169955</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136580334</v>
+        <v>136067673</v>
       </c>
       <c r="B3" t="n">
-        <v>89295</v>
+        <v>92331</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4388</v>
+        <v>3298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mönjevaxing</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hygrocybe miniata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) P.Kumm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -857,22 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,16 +898,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136580334</t>
+          <t>https://artportalen.se/Sighting/136067673</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134163651</v>
+        <v>136580334</v>
       </c>
       <c r="B4" t="n">
-        <v>56915</v>
+        <v>89295</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100088</v>
+        <v>4388</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Mönjevaxing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Hygrocybe miniata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) P.Kumm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -969,22 +969,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,16 +1010,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134163651</t>
+          <t>https://artportalen.se/Sighting/136580334</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127932727</v>
+        <v>134163651</v>
       </c>
       <c r="B5" t="n">
-        <v>56830</v>
+        <v>56915</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,51 +1027,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100092</v>
+        <v>100088</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>ultraljudsdetektor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Halledal, Halledal, Vg</t>
+          <t>Halledal, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>407953</v>
+        <v>407870</v>
       </c>
       <c r="R5" t="n">
-        <v>6393150</v>
+        <v>6393156</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,22 +1081,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>21:44</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>21:44</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,27 +1111,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Persson</t>
+          <t>Dennis Hägg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Persson, Karin Alsing</t>
+          <t>Dennis Hägg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127932727</t>
+          <t>https://artportalen.se/Sighting/134163651</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134148430</v>
+        <v>127932727</v>
       </c>
       <c r="B6" t="n">
-        <v>58151</v>
+        <v>56830</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,37 +1139,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102623</v>
+        <v>100092</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>ultraljudsdetektor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Halledal, Vg</t>
+          <t>Halledal, Halledal, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>407870</v>
+        <v>407953</v>
       </c>
       <c r="R6" t="n">
-        <v>6393156</v>
+        <v>6393150</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1207,12 +1207,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>21:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>21:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1227,49 +1237,49 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Dennis Hägg</t>
+          <t>Håkan Persson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Dennis Hägg</t>
+          <t>Håkan Persson, Karin Alsing</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134148430</t>
+          <t>https://artportalen.se/Sighting/127932727</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134148397</v>
+        <v>134148430</v>
       </c>
       <c r="B7" t="n">
-        <v>57391</v>
+        <v>58151</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102961</v>
+        <v>102623</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1340,16 +1350,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134148397</t>
+          <t>https://artportalen.se/Sighting/134148430</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134148318</v>
+        <v>134148397</v>
       </c>
       <c r="B8" t="n">
-        <v>58519</v>
+        <v>57391</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,21 +1367,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102990</v>
+        <v>102961</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1411,12 +1421,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,38 +1452,38 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134148318</t>
+          <t>https://artportalen.se/Sighting/134148397</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134148406</v>
+        <v>134148318</v>
       </c>
       <c r="B9" t="n">
-        <v>58461</v>
+        <v>58519</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103018</v>
+        <v>102990</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1513,12 +1523,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1544,16 +1554,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134148406</t>
+          <t>https://artportalen.se/Sighting/134148318</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134148542</v>
+        <v>134148406</v>
       </c>
       <c r="B10" t="n">
-        <v>58250</v>
+        <v>58461</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,21 +1571,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103019</v>
+        <v>103018</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stjärtmes</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Aegithalos caudatus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1615,12 +1625,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1646,38 +1656,38 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134148542</t>
+          <t>https://artportalen.se/Sighting/134148406</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135834801</v>
+        <v>134148542</v>
       </c>
       <c r="B11" t="n">
-        <v>43250</v>
+        <v>58250</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>201028</v>
+        <v>103019</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre tåtelsmygare</t>
+          <t>Stjärtmes</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Thymelicus lineola</t>
+          <t>Aegithalos caudatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ochsenheimer, 1808)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1717,22 +1727,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:42</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:42</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1758,38 +1758,38 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135834801</t>
+          <t>https://artportalen.se/Sighting/134148542</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134167265</v>
+        <v>135834801</v>
       </c>
       <c r="B12" t="n">
-        <v>43383</v>
+        <v>43250</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>201075</v>
+        <v>201028</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Mindre tåtelsmygare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Boloria selene</t>
+          <t>Thymelicus lineola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Ochsenheimer, 1808)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1829,22 +1829,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1870,55 +1870,41 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134167265</t>
+          <t>https://artportalen.se/Sighting/135834801</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>108015436</v>
+        <v>134167265</v>
       </c>
       <c r="B13" t="n">
-        <v>58817</v>
+        <v>43383</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>208249</v>
+        <v>201075</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Boloria selene</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Halledal, Vg</t>
@@ -1955,12 +1941,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-04-09</t>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-04-09</t>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1986,16 +1982,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108015436</t>
+          <t>https://artportalen.se/Sighting/134167265</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>108226085</v>
+        <v>108015436</v>
       </c>
       <c r="B14" t="n">
-        <v>56876</v>
+        <v>58817</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2003,16 +1999,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>208257</v>
+        <v>208249</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2022,10 +2018,19 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Halledal, Vg</t>
@@ -2062,22 +2067,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>17:45</t>
+          <t>2023-04-09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>17:45</t>
+          <t>2023-04-09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2103,16 +2098,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108226085</t>
+          <t>https://artportalen.se/Sighting/108015436</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134147585</v>
+        <v>108226085</v>
       </c>
       <c r="B15" t="n">
-        <v>56925</v>
+        <v>56876</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,24 +2115,29 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>208260</v>
+        <v>208257</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Halledal, Vg</t>
@@ -2174,12 +2174,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2023-04-17</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2023-04-17</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2205,16 +2215,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134147585</t>
+          <t>https://artportalen.se/Sighting/108226085</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134174742</v>
+        <v>134147585</v>
       </c>
       <c r="B16" t="n">
-        <v>98219</v>
+        <v>56925</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2222,21 +2232,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219815</v>
+        <v>208260</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2276,22 +2286,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>17:23</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>17:23</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2317,16 +2317,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134174742</t>
+          <t>https://artportalen.se/Sighting/134147585</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134147414</v>
+        <v>134174742</v>
       </c>
       <c r="B17" t="n">
-        <v>99233</v>
+        <v>98219</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2334,21 +2334,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219875</v>
+        <v>219815</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2388,12 +2388,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2419,16 +2429,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134147414</t>
+          <t>https://artportalen.se/Sighting/134174742</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134206667</v>
+        <v>134147414</v>
       </c>
       <c r="B18" t="n">
-        <v>99099</v>
+        <v>99233</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2436,53 +2446,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220093</v>
+        <v>219875</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Halledal, Vg</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>407869</v>
+        <v>407870</v>
       </c>
       <c r="R18" t="n">
-        <v>6393158</v>
+        <v>6393156</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2506,22 +2500,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>17:19</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>17:20</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2536,65 +2520,81 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Matilda Chocron</t>
+          <t>Dennis Hägg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Matilda Chocron</t>
+          <t>Dennis Hägg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134206667</t>
+          <t>https://artportalen.se/Sighting/134147414</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134292011</v>
+        <v>134206667</v>
       </c>
       <c r="B19" t="n">
-        <v>106894</v>
+        <v>99099</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220785</v>
+        <v>220093</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Halledal, Vg</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>407870</v>
+        <v>407869</v>
       </c>
       <c r="R19" t="n">
-        <v>6393156</v>
+        <v>6393158</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>20:47</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>20:47</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2648,44 +2648,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Dennis Hägg</t>
+          <t>Matilda Chocron</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Dennis Hägg</t>
+          <t>Matilda Chocron</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134292011</t>
+          <t>https://artportalen.se/Sighting/134206667</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134147204</v>
+        <v>134292011</v>
       </c>
       <c r="B20" t="n">
-        <v>107695</v>
+        <v>106894</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221705</v>
+        <v>220785</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ängskovall</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Melampyrum pratense</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2730,12 +2730,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>20:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>20:47</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2761,16 +2771,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134147204</t>
+          <t>https://artportalen.se/Sighting/134292011</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134147238</v>
+        <v>134147204</v>
       </c>
       <c r="B21" t="n">
-        <v>103764</v>
+        <v>107695</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2778,16 +2788,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222004</v>
+        <v>221705</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kärrviol</t>
+          <t>Ängskovall</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Viola palustris</t>
+          <t>Melampyrum pratense</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2863,16 +2873,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134147238</t>
+          <t>https://artportalen.se/Sighting/134147204</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134147439</v>
+        <v>134147238</v>
       </c>
       <c r="B22" t="n">
-        <v>99472</v>
+        <v>103764</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2880,16 +2890,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222812</v>
+        <v>222004</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Kärrviol</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Viola palustris</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2965,38 +2975,38 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134147439</t>
+          <t>https://artportalen.se/Sighting/134147238</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135728837</v>
+        <v>134147439</v>
       </c>
       <c r="B23" t="n">
-        <v>103609</v>
+        <v>99472</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>223246</v>
+        <v>222812</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Convallaria majalis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3036,22 +3046,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>20:30</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>20:30</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3076,6 +3076,118 @@
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134147439</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135728837</v>
+      </c>
+      <c r="B24" t="n">
+        <v>103609</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Halledal, Vg</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>407870</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6393156</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ulricehamn</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Gällstad</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Dennis Hägg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Dennis Hägg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135728837</t>
         </is>
@@ -3105,6 +3217,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38156-2026 artfynd.xlsx
+++ b/artfynd/A 38156-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137169955</v>
       </c>
       <c r="B2" t="n">
-        <v>89176</v>
+        <v>89178</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136580334</v>
       </c>
       <c r="B4" t="n">
-        <v>89295</v>
+        <v>89297</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38156-2026 artfynd.xlsx
+++ b/artfynd/A 38156-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137169955</v>
       </c>
       <c r="B2" t="n">
-        <v>89178</v>
+        <v>89191</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38156-2026 artfynd.xlsx
+++ b/artfynd/A 38156-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137169955</v>
       </c>
       <c r="B2" t="n">
-        <v>89191</v>
+        <v>89193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38156-2026 artfynd.xlsx
+++ b/artfynd/A 38156-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137169955</v>
       </c>
       <c r="B2" t="n">
-        <v>89193</v>
+        <v>89196</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38156-2026 artfynd.xlsx
+++ b/artfynd/A 38156-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ24"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137169955</v>
       </c>
       <c r="B2" t="n">
-        <v>89196</v>
+        <v>89206</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135834801</v>
+        <v>137296941</v>
       </c>
       <c r="B12" t="n">
-        <v>43250</v>
+        <v>58192</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1775,21 +1775,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>201028</v>
+        <v>103020</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre tåtelsmygare</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Thymelicus lineola</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ochsenheimer, 1808)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1829,22 +1829,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1870,38 +1870,38 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135834801</t>
+          <t>https://artportalen.se/Sighting/137296941</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134167265</v>
+        <v>135834801</v>
       </c>
       <c r="B13" t="n">
-        <v>43383</v>
+        <v>43250</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>201075</v>
+        <v>201028</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Mindre tåtelsmygare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Boloria selene</t>
+          <t>Thymelicus lineola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Ochsenheimer, 1808)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1941,22 +1941,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1982,55 +1982,41 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134167265</t>
+          <t>https://artportalen.se/Sighting/135834801</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>108015436</v>
+        <v>134167265</v>
       </c>
       <c r="B14" t="n">
-        <v>58817</v>
+        <v>43383</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>208249</v>
+        <v>201075</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Boloria selene</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Halledal, Vg</t>
@@ -2067,12 +2053,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-04-09</t>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-04-09</t>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2098,16 +2094,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108015436</t>
+          <t>https://artportalen.se/Sighting/134167265</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>108226085</v>
+        <v>108015436</v>
       </c>
       <c r="B15" t="n">
-        <v>56876</v>
+        <v>58817</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2115,16 +2111,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>208257</v>
+        <v>208249</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2134,10 +2130,19 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Halledal, Vg</t>
@@ -2174,22 +2179,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>17:45</t>
+          <t>2023-04-09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>17:45</t>
+          <t>2023-04-09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2215,16 +2210,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108226085</t>
+          <t>https://artportalen.se/Sighting/108015436</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134147585</v>
+        <v>108226085</v>
       </c>
       <c r="B16" t="n">
-        <v>56925</v>
+        <v>56876</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2232,24 +2227,29 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>208260</v>
+        <v>208257</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Halledal, Vg</t>
@@ -2286,12 +2286,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2023-04-17</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2023-04-17</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2317,16 +2327,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134147585</t>
+          <t>https://artportalen.se/Sighting/108226085</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134174742</v>
+        <v>134147585</v>
       </c>
       <c r="B17" t="n">
-        <v>98219</v>
+        <v>56925</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2334,21 +2344,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219815</v>
+        <v>208260</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2388,22 +2398,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>17:23</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>17:23</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2429,16 +2429,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134174742</t>
+          <t>https://artportalen.se/Sighting/134147585</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134147414</v>
+        <v>134174742</v>
       </c>
       <c r="B18" t="n">
-        <v>99233</v>
+        <v>98219</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2446,21 +2446,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219875</v>
+        <v>219815</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2500,12 +2500,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2531,16 +2541,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134147414</t>
+          <t>https://artportalen.se/Sighting/134174742</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134206667</v>
+        <v>134147414</v>
       </c>
       <c r="B19" t="n">
-        <v>99099</v>
+        <v>99233</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2548,53 +2558,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220093</v>
+        <v>219875</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Halledal, Vg</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>407869</v>
+        <v>407870</v>
       </c>
       <c r="R19" t="n">
-        <v>6393158</v>
+        <v>6393156</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2618,22 +2612,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>17:19</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>17:20</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2648,65 +2632,81 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Matilda Chocron</t>
+          <t>Dennis Hägg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Matilda Chocron</t>
+          <t>Dennis Hägg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134206667</t>
+          <t>https://artportalen.se/Sighting/134147414</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134292011</v>
+        <v>134206667</v>
       </c>
       <c r="B20" t="n">
-        <v>106894</v>
+        <v>99099</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220785</v>
+        <v>220093</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Halledal, Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>407870</v>
+        <v>407869</v>
       </c>
       <c r="R20" t="n">
-        <v>6393156</v>
+        <v>6393158</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2730,22 +2730,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>20:47</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>20:47</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2760,44 +2760,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Dennis Hägg</t>
+          <t>Matilda Chocron</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Dennis Hägg</t>
+          <t>Matilda Chocron</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134292011</t>
+          <t>https://artportalen.se/Sighting/134206667</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134147204</v>
+        <v>134292011</v>
       </c>
       <c r="B21" t="n">
-        <v>107695</v>
+        <v>106894</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221705</v>
+        <v>220785</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ängskovall</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Melampyrum pratense</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2842,12 +2842,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>20:47</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>20:47</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2873,16 +2883,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134147204</t>
+          <t>https://artportalen.se/Sighting/134292011</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134147238</v>
+        <v>134147204</v>
       </c>
       <c r="B22" t="n">
-        <v>103764</v>
+        <v>107695</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2890,16 +2900,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222004</v>
+        <v>221705</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kärrviol</t>
+          <t>Ängskovall</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Viola palustris</t>
+          <t>Melampyrum pratense</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2975,16 +2985,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134147238</t>
+          <t>https://artportalen.se/Sighting/134147204</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134147439</v>
+        <v>134147238</v>
       </c>
       <c r="B23" t="n">
-        <v>99472</v>
+        <v>103764</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2992,16 +3002,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222812</v>
+        <v>222004</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Kärrviol</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Viola palustris</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3077,38 +3087,38 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134147439</t>
+          <t>https://artportalen.se/Sighting/134147238</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135728837</v>
+        <v>134147439</v>
       </c>
       <c r="B24" t="n">
-        <v>103609</v>
+        <v>99472</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>223246</v>
+        <v>222812</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Convallaria majalis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3148,22 +3158,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>20:30</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>20:30</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3188,6 +3188,118 @@
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134147439</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135728837</v>
+      </c>
+      <c r="B25" t="n">
+        <v>103609</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Halledal, Vg</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>407870</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6393156</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ulricehamn</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Gällstad</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Dennis Hägg</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Dennis Hägg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135728837</t>
         </is>
@@ -3218,6 +3330,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38156-2026 artfynd.xlsx
+++ b/artfynd/A 38156-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137169955</v>
       </c>
       <c r="B2" t="n">
-        <v>89206</v>
+        <v>89207</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38156-2026 artfynd.xlsx
+++ b/artfynd/A 38156-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137169955</v>
       </c>
       <c r="B2" t="n">
-        <v>89207</v>
+        <v>89210</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>137296941</v>
       </c>
       <c r="B12" t="n">
-        <v>58192</v>
+        <v>58193</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 38156-2026 artfynd.xlsx
+++ b/artfynd/A 38156-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137169955</v>
       </c>
       <c r="B2" t="n">
-        <v>89210</v>
+        <v>89215</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>137296941</v>
       </c>
       <c r="B12" t="n">
-        <v>58193</v>
+        <v>58194</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 38156-2026 artfynd.xlsx
+++ b/artfynd/A 38156-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137169955</v>
       </c>
       <c r="B2" t="n">
-        <v>89215</v>
+        <v>89226</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38156-2026 artfynd.xlsx
+++ b/artfynd/A 38156-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137169955</v>
       </c>
       <c r="B2" t="n">
-        <v>89226</v>
+        <v>89227</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38156-2026 artfynd.xlsx
+++ b/artfynd/A 38156-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137169955</v>
       </c>
       <c r="B2" t="n">
-        <v>89227</v>
+        <v>89230</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38156-2026 artfynd.xlsx
+++ b/artfynd/A 38156-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137169955</v>
       </c>
       <c r="B2" t="n">
-        <v>89230</v>
+        <v>89234</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>137296941</v>
       </c>
       <c r="B12" t="n">
-        <v>58194</v>
+        <v>58197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
